--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T1_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T1_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.253</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>0.396</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.143</t>
-  </si>
-  <si>
-    <t>(0.037)</t>
-  </si>
-  <si>
-    <t>0.549</t>
-  </si>
-  <si>
-    <t>(0.160)</t>
-  </si>
-  <si>
-    <t>0.758</t>
-  </si>
-  <si>
-    <t>(0.132)</t>
-  </si>
-  <si>
-    <t>0.187</t>
-  </si>
-  <si>
-    <t>(0.058)</t>
+    <t>0.264</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>0.414</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>0.149</t>
+  </si>
+  <si>
+    <t>(0.038)</t>
+  </si>
+  <si>
+    <t>0.575</t>
+  </si>
+  <si>
+    <t>(0.166)</t>
+  </si>
+  <si>
+    <t>0.793</t>
+  </si>
+  <si>
+    <t>(0.137)</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
   </si>
   <si>
     <t>23</t>
@@ -138,7 +138,7 @@
     <t>(0.151)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>0.387***</t>
-  </si>
-  <si>
-    <t>0.335***</t>
-  </si>
-  <si>
-    <t>0.494</t>
-  </si>
-  <si>
-    <t>1.763***</t>
-  </si>
-  <si>
-    <t>0.422***</t>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>0.369***</t>
+  </si>
+  <si>
+    <t>0.329***</t>
+  </si>
+  <si>
+    <t>0.469</t>
+  </si>
+  <si>
+    <t>1.729***</t>
+  </si>
+  <si>
+    <t>0.413***</t>
   </si>
 </sst>
 </file>
